--- a/artfynd/A 5863-2026 artfynd.xlsx
+++ b/artfynd/A 5863-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1829,6 +1829,2528 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>134624644</v>
+      </c>
+      <c r="B12" t="n">
+        <v>43472</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Hejde Väntinge, Gtl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>699769</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6365608</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Hejde</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>16:13</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>16:13</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>5 st</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen, Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>134624645</v>
+      </c>
+      <c r="B13" t="n">
+        <v>43472</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Hejde Väntinge, Gtl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>699772</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6365575</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Hejde</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>16:14</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>16:14</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>4 st</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen, Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>134624647</v>
+      </c>
+      <c r="B14" t="n">
+        <v>43472</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Hejde Väntinge, Gtl</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>699787</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6365560</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Hejde</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>16:16</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>16:16</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen, Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>134624648</v>
+      </c>
+      <c r="B15" t="n">
+        <v>43472</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Hejde Väntinge, Gtl</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>699790</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6365560</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Hejde</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>16:17</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>16:17</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>2 st</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen, Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>134624649</v>
+      </c>
+      <c r="B16" t="n">
+        <v>43472</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Hejde Väntinge, Gtl</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>699800</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6365576</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Hejde</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>16:18</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>16:18</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen, Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>134624650</v>
+      </c>
+      <c r="B17" t="n">
+        <v>43472</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Hejde Väntinge, Gtl</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>699814</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6365571</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Hejde</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>16:18</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>16:18</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen, Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>134624652</v>
+      </c>
+      <c r="B18" t="n">
+        <v>43472</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Hejde Väntinge, Gtl</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>699801</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6365546</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Hejde</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>3 st</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen, Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>134624654</v>
+      </c>
+      <c r="B19" t="n">
+        <v>43472</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Hejde Väntinge, Gtl</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>699799</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6365530</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Hejde</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>2 st</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen, Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>134624655</v>
+      </c>
+      <c r="B20" t="n">
+        <v>43472</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Hejde Väntinge, Gtl</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>699810</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6365508</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Hejde</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>16:23</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>16:23</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen, Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>134624656</v>
+      </c>
+      <c r="B21" t="n">
+        <v>43472</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Hejde Väntinge, Gtl</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>699791</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6365501</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Hejde</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>16:24</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>16:24</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen, Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>134624658</v>
+      </c>
+      <c r="B22" t="n">
+        <v>43472</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Hejde Väntinge, Gtl</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>699756</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6365519</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Hejde</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>16:27</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>16:27</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>2 st.</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen, Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>134624661</v>
+      </c>
+      <c r="B23" t="n">
+        <v>43472</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Hejde Väntinge, Gtl</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>699727</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6365544</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Hejde</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>16:28</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>16:28</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>3 st</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen, Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>134624663</v>
+      </c>
+      <c r="B24" t="n">
+        <v>43472</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Hejde Väntinge, Gtl</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>699734</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6365556</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Hejde</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen, Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>134624664</v>
+      </c>
+      <c r="B25" t="n">
+        <v>43472</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Hejde Väntinge, Gtl</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>699741</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6365547</v>
+      </c>
+      <c r="S25" t="n">
+        <v>5</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Hejde</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>16:31</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>16:31</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen, Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>134624665</v>
+      </c>
+      <c r="B26" t="n">
+        <v>43472</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Hejde Väntinge, Gtl</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>699726</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6365569</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Hejde</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>16:32</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>16:32</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen, Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>134624668</v>
+      </c>
+      <c r="B27" t="n">
+        <v>43472</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Hejde Väntinge, Gtl</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>699725</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6365584</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Hejde</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>16:33</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>16:33</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen, Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>134624669</v>
+      </c>
+      <c r="B28" t="n">
+        <v>43472</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Hejde Väntinge, Gtl</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>699724</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6365601</v>
+      </c>
+      <c r="S28" t="n">
+        <v>6</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Hejde</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>16:35</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>16:35</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>2 st</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen, Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>134624670</v>
+      </c>
+      <c r="B29" t="n">
+        <v>43472</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Hejde Väntinge, Gtl</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>699747</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6365626</v>
+      </c>
+      <c r="S29" t="n">
+        <v>5</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Hejde</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>16:36</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>16:36</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen, Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>134624671</v>
+      </c>
+      <c r="B30" t="n">
+        <v>43472</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Hejde Väntinge, Gtl</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>699749</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6365634</v>
+      </c>
+      <c r="S30" t="n">
+        <v>5</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Hejde</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>16:37</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>16:37</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>3 st</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen, Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>134624672</v>
+      </c>
+      <c r="B31" t="n">
+        <v>43472</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Hejde Väntinge, Gtl</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>699755</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6365634</v>
+      </c>
+      <c r="S31" t="n">
+        <v>5</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Hejde</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>16:38</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>16:38</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen, Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>134624675</v>
+      </c>
+      <c r="B32" t="n">
+        <v>43472</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Hejde Väntinge, Gtl</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>699763</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6365665</v>
+      </c>
+      <c r="S32" t="n">
+        <v>5</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Hejde</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>16:41</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>16:41</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>3 st</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen, Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>134624676</v>
+      </c>
+      <c r="B33" t="n">
+        <v>43472</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Hejde Väntinge, Gtl</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>699743</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6365663</v>
+      </c>
+      <c r="S33" t="n">
+        <v>5</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Hejde</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>16:41</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>16:41</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen, Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>134624677</v>
+      </c>
+      <c r="B34" t="n">
+        <v>43472</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Hejde Väntinge, Gtl</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>699784</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6365691</v>
+      </c>
+      <c r="S34" t="n">
+        <v>5</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Hejde</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>16:44</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>16:44</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>2 st</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen, Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 5863-2026 artfynd.xlsx
+++ b/artfynd/A 5863-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY34"/>
+  <dimension ref="A1:AZ34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -786,6 +791,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62415524</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -904,6 +914,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68570288</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1023,6 +1038,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79993313</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1138,6 +1158,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88788450</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1253,6 +1278,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95565577</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1368,6 +1398,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103833930</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1483,6 +1518,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111748634</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1598,6 +1638,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111748757</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1713,6 +1758,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119203315</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1828,6 +1878,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119203325</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1940,6 +1995,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134624644</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2052,6 +2112,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134624645</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2159,6 +2224,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134624647</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2271,6 +2341,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134624648</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2378,6 +2453,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134624649</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2485,6 +2565,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134624650</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2597,6 +2682,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134624652</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2709,6 +2799,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134624654</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2816,6 +2911,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134624655</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2923,6 +3023,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134624656</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3041,6 +3146,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134624658</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3153,6 +3263,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134624661</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3260,6 +3375,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134624663</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3367,6 +3487,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134624664</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3474,6 +3599,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134624665</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3581,6 +3711,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134624668</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3693,6 +3828,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134624669</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3800,6 +3940,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134624670</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3912,6 +4057,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134624671</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4019,6 +4169,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134624672</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4131,6 +4286,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134624675</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4238,6 +4398,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134624676</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4350,8 +4515,48 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134624677</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>